--- a/users_list.xlsx
+++ b/users_list.xlsx
@@ -9,21 +9,23 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Himanshu S" sheetId="2" r:id="rId2"/>
-    <sheet name="Onkar L" sheetId="3" r:id="rId3"/>
-    <sheet name="Abhishek S" sheetId="4" r:id="rId4"/>
-    <sheet name="Skip" sheetId="5" r:id="rId5"/>
+    <sheet name="Onkar" sheetId="6" r:id="rId2"/>
+    <sheet name="Pranav" sheetId="7" r:id="rId3"/>
+    <sheet name="Himanshu" sheetId="8" r:id="rId4"/>
+    <sheet name="Abhishek" sheetId="9" r:id="rId5"/>
+    <sheet name="Mehul" sheetId="10" r:id="rId6"/>
+    <sheet name="Skip" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="6">
   <si>
     <t>Name</t>
   </si>
@@ -441,16 +443,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="8.88671875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.21875" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" customWidth="1"/>
-    <col min="6" max="6" width="21.5546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="43" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" customWidth="1"/>
+    <col min="3" max="3" width="23.109375" customWidth="1"/>
+    <col min="4" max="4" width="20.109375" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" customWidth="1"/>
+    <col min="6" max="6" width="36.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.6" customHeight="1">
+    <row r="1" spans="1:6" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -469,10 +473,9 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -481,13 +484,15 @@
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="3" max="3" width="8.88671875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" customWidth="1"/>
-    <col min="5" max="5" width="18.77734375" customWidth="1"/>
-    <col min="6" max="6" width="21.77734375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="36.21875" customWidth="1"/>
+    <col min="2" max="2" width="18.33203125" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="25.88671875" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" customHeight="1">
+    <row r="1" spans="1:6" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -508,7 +513,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -517,15 +522,15 @@
   <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" customWidth="1"/>
-    <col min="4" max="4" width="24.21875" customWidth="1"/>
-    <col min="5" max="5" width="26.77734375" customWidth="1"/>
-    <col min="6" max="6" width="16.21875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="27.77734375" customWidth="1"/>
+    <col min="2" max="2" width="16.21875" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="5" width="20.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.2" customHeight="1">
+    <row r="1" spans="1:6" ht="15.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -552,7 +557,83 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="2" max="2" width="20.5546875" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" customWidth="1"/>
+    <col min="4" max="4" width="22.109375" customWidth="1"/>
+    <col min="5" max="5" width="21.77734375" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="27.6640625" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="4" max="4" width="20.5546875" customWidth="1"/>
+    <col min="5" max="5" width="21.5546875" customWidth="1"/>
+    <col min="6" max="6" width="17.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="8.88671875" style="2" customWidth="1"/>
@@ -581,6 +662,15 @@
       </c>
       <c r="G1" s="1"/>
     </row>
+    <row r="2" spans="1:7">
+      <c r="C2"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="C3"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="C4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
